--- a/output/pdf_financials_xlsx/DAN.xlsx
+++ b/output/pdf_financials_xlsx/DAN.xlsx
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.587649</v>
+        <v>-21.860377</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.131489</v>
+        <v>-18.071027</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.170529</v>
+        <v>-1.567683</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>21.985953</v>
+        <v>0.004515</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -869,16 +869,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>11.224013</v>
+        <v>-11.224013</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9.101258</v>
+        <v>-9.101258</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.698577</v>
+        <v>-0.698577</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>10.990719</v>
+        <v>-10.990719</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>11.224013</v>
+        <v>-11.224013</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>9.101258</v>
+        <v>-9.101258</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.698577</v>
+        <v>-0.698577</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>10.990719</v>
+        <v>-10.990719</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>0.042177</v>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-160.343043</v>
+        <v>160.343043</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-182.02516</v>
+        <v>182.02516</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>219.81438</v>
+        <v>-219.81438</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5.524904939319489</v>
+        <v>205.5249049393195</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1.465912890287364</v>
+        <v>201.4659128902874</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>19.62119695411147</v>
+        <v>180.3788030458885</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-199.9589367538699</v>
+        <v>-0.041063246130096</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
@@ -7216,16 +7216,16 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>11.224013</v>
+        <v>-11.224013</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>9.101258</v>
+        <v>-9.101258</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.698577</v>
+        <v>-0.698577</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>10.990719</v>
+        <v>-10.990719</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/DAN.xlsx
+++ b/output/pdf_financials_xlsx/DAN.xlsx
@@ -673,16 +673,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011297</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.088307</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.164453</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.102335</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1033,16 +1033,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10.66963</v>
+        <v>10.680927</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8.990265000000001</v>
+        <v>9.078571999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.886032</v>
+        <v>1.050485</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-10.985279</v>
+        <v>-10.882944</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.042177</v>
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>10.66963</v>
+        <v>10.680927</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8.990265000000001</v>
+        <v>9.078571999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.886032</v>
+        <v>1.050485</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-10.985279</v>
+        <v>-10.882944</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0.042177</v>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">

--- a/output/pdf_financials_xlsx/DAN.xlsx
+++ b/output/pdf_financials_xlsx/DAN.xlsx
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.3368</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -5981,7 +5981,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>0.3368</v>
       </c>
